--- a/Inventario IP.xlsx
+++ b/Inventario IP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas.g\projetos\pingador\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95C324B4-A606-454D-BB5E-530A9CA890AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97527B99-1E5A-4431-B263-C4250E4F2F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="6" xr2:uid="{4F6266B4-2EA0-453D-9E98-FB6A2BABF4B3}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F6266B4-2EA0-453D-9E98-FB6A2BABF4B3}"/>
   </bookViews>
   <sheets>
     <sheet name="Geral" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="Diversos" sheetId="8" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Geral!$A$1:$G$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Geral!$A$1:$G$160</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Impressoras!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="264">
   <si>
     <t>IP</t>
   </si>
@@ -857,6 +857,15 @@
   <si>
     <t>PB escritório</t>
   </si>
+  <si>
+    <t>172.16.190.253</t>
+  </si>
+  <si>
+    <t>Yorozu@2026#</t>
+  </si>
+  <si>
+    <t>Acess point para testes de rede com o wifi YOROZU-TI</t>
+  </si>
 </sst>
 </file>
 
@@ -1017,7 +1026,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1044,12 +1053,37 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="24">
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <border>
         <left style="thin">
@@ -1671,7 +1705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55A70348-D7B3-424F-BEF3-43EAC088AF88}">
-  <dimension ref="A1:W1002"/>
+  <dimension ref="A1:W1003"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
@@ -1741,7 +1775,7 @@
         <v>14</v>
       </c>
       <c r="W2" t="str" cm="1">
-        <f t="array" ref="W2:W8">_xlfn.VSTACK(_xlfn.UNIQUE(_xlfn._xlws.FILTER($J$2:$J$1001,$J$2:$J$1001&lt;&gt;"")),"Diversos")</f>
+        <f t="array" ref="W2:W8">_xlfn.VSTACK(_xlfn.UNIQUE(_xlfn._xlws.FILTER($J$2:$J$1002,$J$2:$J$1002&lt;&gt;"")),"Diversos")</f>
         <v>Rede e Segurança</v>
       </c>
     </row>
@@ -3345,37 +3379,37 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>178</v>
+        <v>261</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>179</v>
+        <v>25</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="D86" s="5"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="5"/>
+      <c r="E86" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>263</v>
+      </c>
       <c r="G86" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>41</v>
+        <v>179</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>43</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="D87" s="5"/>
+      <c r="E87" s="5"/>
       <c r="F87" s="5"/>
       <c r="G87" s="2" t="s">
         <v>30</v>
@@ -3383,10 +3417,10 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>22</v>
@@ -3395,7 +3429,7 @@
         <v>42</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>183</v>
+        <v>43</v>
       </c>
       <c r="F88" s="5"/>
       <c r="G88" s="2" t="s">
@@ -3404,7 +3438,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>29</v>
@@ -3412,8 +3446,12 @@
       <c r="C89" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D89" s="5"/>
-      <c r="E89" s="5"/>
+      <c r="D89" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>183</v>
+      </c>
       <c r="F89" s="5"/>
       <c r="G89" s="2" t="s">
         <v>30</v>
@@ -3421,7 +3459,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>29</v>
@@ -3438,7 +3476,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>29</v>
@@ -3455,7 +3493,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>29</v>
@@ -3472,7 +3510,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>29</v>
@@ -3480,12 +3518,8 @@
       <c r="C93" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D93" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E93" t="s">
-        <v>183</v>
-      </c>
+      <c r="D93" s="5"/>
+      <c r="E93" s="5"/>
       <c r="F93" s="5"/>
       <c r="G93" s="2" t="s">
         <v>30</v>
@@ -3493,7 +3527,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>29</v>
@@ -3501,8 +3535,12 @@
       <c r="C94" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D94" s="5"/>
-      <c r="E94" s="5"/>
+      <c r="D94" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E94" t="s">
+        <v>183</v>
+      </c>
       <c r="F94" s="5"/>
       <c r="G94" s="2" t="s">
         <v>30</v>
@@ -3510,7 +3548,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>29</v>
@@ -3518,12 +3556,8 @@
       <c r="C95" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D95" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E95" t="s">
-        <v>183</v>
-      </c>
+      <c r="D95" s="5"/>
+      <c r="E95" s="5"/>
       <c r="F95" s="5"/>
       <c r="G95" s="2" t="s">
         <v>30</v>
@@ -3531,7 +3565,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>29</v>
@@ -3542,7 +3576,7 @@
       <c r="D96" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E96" s="5" t="s">
+      <c r="E96" t="s">
         <v>183</v>
       </c>
       <c r="F96" s="5"/>
@@ -3552,7 +3586,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>29</v>
@@ -3560,8 +3594,12 @@
       <c r="C97" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D97" s="5"/>
-      <c r="E97" s="5"/>
+      <c r="D97" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>183</v>
+      </c>
       <c r="F97" s="5"/>
       <c r="G97" s="2" t="s">
         <v>30</v>
@@ -3569,7 +3607,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>29</v>
@@ -3577,12 +3615,8 @@
       <c r="C98" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D98" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>183</v>
-      </c>
+      <c r="D98" s="5"/>
+      <c r="E98" s="5"/>
       <c r="F98" s="5"/>
       <c r="G98" s="2" t="s">
         <v>30</v>
@@ -3590,7 +3624,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>29</v>
@@ -3611,7 +3645,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>29</v>
@@ -3632,7 +3666,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>29</v>
@@ -3653,7 +3687,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>29</v>
@@ -3674,7 +3708,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>29</v>
@@ -3695,7 +3729,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>29</v>
@@ -3716,7 +3750,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>29</v>
@@ -3737,7 +3771,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>29</v>
@@ -3758,7 +3792,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>29</v>
@@ -3779,7 +3813,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>29</v>
@@ -3800,7 +3834,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>29</v>
@@ -3821,7 +3855,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>29</v>
@@ -3842,7 +3876,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>29</v>
@@ -3863,7 +3897,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>29</v>
@@ -3884,7 +3918,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>29</v>
@@ -3905,7 +3939,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>29</v>
@@ -3926,7 +3960,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>29</v>
@@ -3947,7 +3981,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>29</v>
@@ -3968,7 +4002,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>29</v>
@@ -3989,7 +4023,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>29</v>
@@ -4010,7 +4044,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>29</v>
@@ -4031,7 +4065,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>29</v>
@@ -4052,7 +4086,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>29</v>
@@ -4073,7 +4107,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>29</v>
@@ -4094,7 +4128,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>29</v>
@@ -4115,7 +4149,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>29</v>
@@ -4136,7 +4170,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>29</v>
@@ -4157,7 +4191,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>29</v>
@@ -4178,7 +4212,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>29</v>
@@ -4199,7 +4233,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>29</v>
@@ -4220,7 +4254,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>29</v>
@@ -4232,7 +4266,7 @@
         <v>42</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>43</v>
+        <v>183</v>
       </c>
       <c r="F129" s="5"/>
       <c r="G129" s="2" t="s">
@@ -4241,7 +4275,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>29</v>
@@ -4253,7 +4287,7 @@
         <v>42</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>183</v>
+        <v>43</v>
       </c>
       <c r="F130" s="5"/>
       <c r="G130" s="2" t="s">
@@ -4262,7 +4296,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>29</v>
@@ -4274,7 +4308,7 @@
         <v>42</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>43</v>
+        <v>183</v>
       </c>
       <c r="F131" s="5"/>
       <c r="G131" s="2" t="s">
@@ -4283,7 +4317,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>29</v>
@@ -4295,7 +4329,7 @@
         <v>42</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>183</v>
+        <v>43</v>
       </c>
       <c r="F132" s="5"/>
       <c r="G132" s="2" t="s">
@@ -4304,7 +4338,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>29</v>
@@ -4316,7 +4350,7 @@
         <v>42</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>43</v>
+        <v>183</v>
       </c>
       <c r="F133" s="5"/>
       <c r="G133" s="2" t="s">
@@ -4325,7 +4359,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>29</v>
@@ -4337,7 +4371,7 @@
         <v>42</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>183</v>
+        <v>43</v>
       </c>
       <c r="F134" s="5"/>
       <c r="G134" s="2" t="s">
@@ -4346,7 +4380,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>29</v>
@@ -4367,7 +4401,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>29</v>
@@ -4388,7 +4422,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>29</v>
@@ -4409,7 +4443,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>29</v>
@@ -4430,7 +4464,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>29</v>
@@ -4451,7 +4485,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>29</v>
@@ -4472,7 +4506,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>29</v>
@@ -4493,7 +4527,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>29</v>
@@ -4514,7 +4548,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>29</v>
@@ -4535,51 +4569,51 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>240</v>
+        <v>22</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>242</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="F144" s="5"/>
       <c r="G144" s="2" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>22</v>
+        <v>240</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F145" s="5"/>
+        <v>241</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>242</v>
+      </c>
       <c r="G145" s="2" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>29</v>
@@ -4600,7 +4634,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>29</v>
@@ -4621,7 +4655,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>29</v>
@@ -4642,7 +4676,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>29</v>
@@ -4663,7 +4697,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>29</v>
@@ -4675,7 +4709,7 @@
         <v>42</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>43</v>
+        <v>183</v>
       </c>
       <c r="F150" s="5"/>
       <c r="G150" s="2" t="s">
@@ -4684,7 +4718,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>29</v>
@@ -4705,7 +4739,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>29</v>
@@ -4726,7 +4760,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>29</v>
@@ -4734,8 +4768,12 @@
       <c r="C153" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D153" s="5"/>
-      <c r="E153" s="5"/>
+      <c r="D153" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E153" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="F153" s="5"/>
       <c r="G153" s="2" t="s">
         <v>30</v>
@@ -4743,7 +4781,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B154" s="5" t="s">
         <v>29</v>
@@ -4751,12 +4789,8 @@
       <c r="C154" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D154" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E154" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="D154" s="5"/>
+      <c r="E154" s="5"/>
       <c r="F154" s="5"/>
       <c r="G154" s="2" t="s">
         <v>30</v>
@@ -4764,7 +4798,7 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B155" s="5" t="s">
         <v>29</v>
@@ -4785,7 +4819,7 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B156" s="5" t="s">
         <v>29</v>
@@ -4806,7 +4840,7 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B157" s="5" t="s">
         <v>29</v>
@@ -4827,7 +4861,7 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B158" s="5" t="s">
         <v>29</v>
@@ -4848,7 +4882,7 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B159" s="5" t="s">
         <v>29</v>
@@ -4868,13 +4902,25 @@
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A160" s="3"/>
-      <c r="B160" s="3"/>
-      <c r="C160" s="3"/>
-      <c r="D160" s="3"/>
-      <c r="E160" s="3"/>
-      <c r="F160" s="3"/>
-      <c r="G160" s="9"/>
+      <c r="A160" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D160" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E160" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F160" s="5"/>
+      <c r="G160" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" s="3"/>
@@ -5747,7 +5793,7 @@
       <c r="D257" s="3"/>
       <c r="E257" s="3"/>
       <c r="F257" s="3"/>
-      <c r="G257" s="8"/>
+      <c r="G257" s="9"/>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A258" s="3"/>
@@ -5756,7 +5802,7 @@
       <c r="D258" s="3"/>
       <c r="E258" s="3"/>
       <c r="F258" s="3"/>
-      <c r="G258" s="2"/>
+      <c r="G258" s="8"/>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A259" s="3"/>
@@ -12454,51 +12500,71 @@
       <c r="F1002" s="3"/>
       <c r="G1002" s="2"/>
     </row>
+    <row r="1003" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1003" s="3"/>
+      <c r="B1003" s="3"/>
+      <c r="C1003" s="3"/>
+      <c r="D1003" s="3"/>
+      <c r="E1003" s="3"/>
+      <c r="F1003" s="3"/>
+      <c r="G1003" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G159" xr:uid="{55A70348-D7B3-424F-BEF3-43EAC088AF88}"/>
+  <autoFilter ref="A1:G160" xr:uid="{55A70348-D7B3-424F-BEF3-43EAC088AF88}"/>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="A2:G2 A3:C3 E3:F3 G3:G16 A4:F6 A7:D7 F7 A8:F16 A93:D93 F93:G93 A94:G94 A95:D96 F95:G96 A97:G1002">
-    <cfRule type="expression" dxfId="21" priority="5">
+  <conditionalFormatting sqref="A2:G2 A3:C3 E3:F3 G3:G16 A4:F6 A7:D7 F7 A8:F16 A94:D94 F94:G94 A95:G95 A96:D97 F96:G97 A98:G1003">
+    <cfRule type="expression" dxfId="23" priority="7">
       <formula>AND($A2&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="6">
+    <cfRule type="expression" dxfId="22" priority="8">
       <formula>$A2&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A17:G92">
-    <cfRule type="expression" dxfId="19" priority="1">
+  <conditionalFormatting sqref="A17:G85 A87:G93">
+    <cfRule type="expression" dxfId="21" priority="3">
       <formula>AND($A17&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="2">
+    <cfRule type="expression" dxfId="20" priority="4">
       <formula>$A17&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="17" priority="8">
+    <cfRule type="expression" dxfId="19" priority="10">
       <formula>AND($A3&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="10">
+    <cfRule type="expression" dxfId="18" priority="12">
       <formula>$A3&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E96">
-    <cfRule type="expression" dxfId="15" priority="3">
-      <formula>AND($A96&lt;&gt;"",MOD(ROW(),2)=0)</formula>
+  <conditionalFormatting sqref="E97">
+    <cfRule type="expression" dxfId="17" priority="5">
+      <formula>AND($A97&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="4">
-      <formula>$A96&lt;&gt;""</formula>
+    <cfRule type="expression" dxfId="16" priority="6">
+      <formula>$A97&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A86:G86">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>AND($A86&lt;&gt;"",MOD(ROW(),2)=0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>$A86&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1002" xr:uid="{25A6F946-7D0C-4F25-A379-F3DB5D1B3AB5}">
-      <formula1>OFFSET($I$2,0,0,COUNTA($I$2:$I$1001),1)</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1003" xr:uid="{25A6F946-7D0C-4F25-A379-F3DB5D1B3AB5}">
+      <formula1>OFFSET($I$2,0,0,COUNTA($I$2:$I$1002),1)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1002" xr:uid="{0EA80F28-25A5-486A-BBB0-9C2D140EFC3F}">
-      <formula1>OFFSET($W$2,0,0,COUNTA($W$2:$W$101),1)</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1003" xr:uid="{0EA80F28-25A5-486A-BBB0-9C2D140EFC3F}">
+      <formula1>OFFSET($W$2,0,0,COUNTA($W$2:$W$102),1)</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E86" r:id="rId1" xr:uid="{78C9D49C-0D94-423A-95C7-16083FC7DE23}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -12552,7 +12618,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="str" cm="1">
-        <f t="array" ref="A5:G26">IFERROR(_xlfn._xlws.FILTER(Geral!$A$2:$G$1002&amp;"",(Geral!$A$2:$A$1002&lt;&gt;"")*ISNUMBER(SEARCH($B$1,Geral!$A$2:$A$1002&amp;" "&amp;Geral!$B$2:$B$1002&amp;" "&amp;Geral!$C$2:$C$1002&amp;" "&amp;Geral!$D$2:$D$1002&amp;" "&amp;Geral!$E$2:$E$1002&amp;" "&amp;Geral!$F$2:$F$1002&amp;" "&amp;Geral!$G$2:$G$1002))),"Nenhum resultado")</f>
+        <f t="array" ref="A5:G26">IFERROR(_xlfn._xlws.FILTER(Geral!$A$2:$G$1003&amp;"",(Geral!$A$2:$A$1003&lt;&gt;"")*ISNUMBER(SEARCH($B$1,Geral!$A$2:$A$1003&amp;" "&amp;Geral!$B$2:$B$1003&amp;" "&amp;Geral!$C$2:$C$1003&amp;" "&amp;Geral!$D$2:$D$1003&amp;" "&amp;Geral!$E$2:$E$1003&amp;" "&amp;Geral!$F$2:$F$1003&amp;" "&amp;Geral!$G$2:$G$1003))),"Nenhum resultado")</f>
         <v>172.16.190.1</v>
       </c>
       <c r="B5" t="str">
@@ -13097,7 +13163,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="str" cm="1">
-        <f t="array" ref="A2:F3">IFERROR(_xlfn._xlws.FILTER(Geral!$A$2:$F$1002&amp;"",Geral!$G$2:$G$1002="Rede e Segurança"),"")</f>
+        <f t="array" ref="A2:F3">IFERROR(_xlfn._xlws.FILTER(Geral!$A$2:$F$1003&amp;"",Geral!$G$2:$G$1003="Rede e Segurança"),"")</f>
         <v>172.16.190.89</v>
       </c>
       <c r="B2" s="3" t="str">
@@ -21114,10 +21180,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:F1000">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>AND($A2&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="2">
+    <cfRule type="expression" dxfId="14" priority="2">
       <formula>$A2&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21160,7 +21226,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="str" cm="1">
-        <f t="array" ref="A2:F24">IFERROR(_xlfn._xlws.FILTER(Geral!$A$2:$F$1002&amp;"",Geral!$G$2:$G$1002="Servidores"),"")</f>
+        <f t="array" ref="A2:F24">IFERROR(_xlfn._xlws.FILTER(Geral!$A$2:$F$1003&amp;"",Geral!$G$2:$G$1003="Servidores"),"")</f>
         <v>172.16.190.1</v>
       </c>
       <c r="B2" s="3" t="str">
@@ -29429,10 +29495,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:F1000">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>AND($A2&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="12" priority="2">
       <formula>$A2&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29475,7 +29541,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="str" cm="1">
-        <f t="array" ref="A2:F11">IFERROR(_xlfn._xlws.FILTER(Geral!$A$2:$F$1002&amp;"",Geral!$G$2:$G$1002="Access Points"),"")</f>
+        <f t="array" ref="A2:F12">IFERROR(_xlfn._xlws.FILTER(Geral!$A$2:$F$1003&amp;"",Geral!$G$2:$G$1003="Access Points"),"")</f>
         <v>172.16.190.50</v>
       </c>
       <c r="B2" s="3" t="str">
@@ -29675,12 +29741,24 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="A12" s="3" t="str">
+        <v>172.16.190.253</v>
+      </c>
+      <c r="B12" s="3" t="str">
+        <v>AP</v>
+      </c>
+      <c r="C12" s="3" t="str">
+        <v>Tp-Link</v>
+      </c>
+      <c r="D12" s="3" t="str">
+        <v/>
+      </c>
+      <c r="E12" s="3" t="str">
+        <v>Yorozu@2026#</v>
+      </c>
+      <c r="F12" s="3" t="str">
+        <v>Acess point para testes de rede com o wifi YOROZU-TI</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
@@ -37588,10 +37666,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:F1000">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>AND($A2&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>$A2&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -37635,7 +37713,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="str" cm="1">
-        <f t="array" ref="A2:F89">IFERROR(_xlfn._xlws.FILTER(Geral!$A$2:$F$1002&amp;"",Geral!$G$2:$G$1002="Câmeras"),"")</f>
+        <f t="array" ref="A2:F89">IFERROR(_xlfn._xlws.FILTER(Geral!$A$2:$F$1003&amp;"",Geral!$G$2:$G$1003="Câmeras"),"")</f>
         <v>172.16.190.20</v>
       </c>
       <c r="B2" s="3" t="str">
@@ -46687,10 +46765,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:F1000">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>AND($A2&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>$A2&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46732,7 +46810,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="str" cm="1">
-        <f t="array" ref="A2:F19">IFERROR(_xlfn._xlws.FILTER(Geral!$A$2:$F$1002&amp;"",Geral!$G$2:$G$1002="Impressoras"),"")</f>
+        <f t="array" ref="A2:F19">IFERROR(_xlfn._xlws.FILTER(Geral!$A$2:$F$1003&amp;"",Geral!$G$2:$G$1003="Impressoras"),"")</f>
         <v>172.16.190.30</v>
       </c>
       <c r="B2" s="3" t="str">
@@ -54942,10 +55020,10 @@
   </sheetData>
   <autoFilter ref="A1:F19" xr:uid="{07A44C41-CAB0-4A84-8B83-1AE0EBFC5A43}"/>
   <conditionalFormatting sqref="A2:F1000">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>AND($A2&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>$A2&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54989,7 +55067,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="str" cm="1">
-        <f t="array" ref="A2:F11">IFERROR(_xlfn._xlws.FILTER(Geral!$A$2:$F$1002&amp;"",Geral!$G$2:$G$1002="Controle de Acesso"),"")</f>
+        <f t="array" ref="A2:F11">IFERROR(_xlfn._xlws.FILTER(Geral!$A$2:$F$1003&amp;"",Geral!$G$2:$G$1003="Controle de Acesso"),"")</f>
         <v>172.16.190.90</v>
       </c>
       <c r="B2" s="3" t="str">
@@ -63102,10 +63180,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:F1000">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>AND($A2&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>$A2&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63148,7 +63226,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="str" cm="1">
-        <f t="array" ref="A2:F3">IFERROR(_xlfn._xlws.FILTER(Geral!$A$2:$F$1002&amp;"",Geral!$G$2:$G$1002="Diversos"),"")</f>
+        <f t="array" ref="A2:F3">IFERROR(_xlfn._xlws.FILTER(Geral!$A$2:$F$1003&amp;"",Geral!$G$2:$G$1003="Diversos"),"")</f>
         <v>172.16.190.137</v>
       </c>
       <c r="B2" s="3" t="str">
@@ -71165,10 +71243,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:F1000">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>AND($A2&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>$A2&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
